--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate/AGGREGATE_AMICS CASTELLÓ.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate/AGGREGATE_AMICS CASTELLÓ.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>364.48</v>
+        <v>441.08</v>
       </c>
       <c r="C2" t="n">
-        <v>365.7</v>
+        <v>442.16</v>
       </c>
       <c r="D2" t="n">
-        <v>103.6368608148756</v>
+        <v>100.6423014293468</v>
       </c>
       <c r="E2" t="n">
-        <v>103.9103089964452</v>
+        <v>101.3207888547132</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4853420195439739</v>
+        <v>0.473474801061008</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1653161963304461</v>
+        <v>0.1618247668952763</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3439153439153439</v>
+        <v>0.3305084745762712</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2638436482084691</v>
+        <v>0.23342175066313</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L2" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="M2" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="O2" t="n">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3420195439739414</v>
+        <v>0.3554376657824934</v>
       </c>
       <c r="Q2" t="n">
         <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1172638436482085</v>
+        <v>0.1007957559681698</v>
       </c>
       <c r="T2" t="n">
         <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05537459283387622</v>
+        <v>0.04774535809018567</v>
       </c>
       <c r="W2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="X2" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1791530944625407</v>
+        <v>0.1830238726790451</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3061889250814332</v>
+        <v>0.3129973474801061</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.5223880597014925</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3454545454545455</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3085106382978723</v>
+        <v>0.3050847457627119</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.028571428571428</v>
+        <v>1.044776119402985</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9664429530201343</v>
+        <v>0.9144385026737968</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6329113924050633</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.62962962962963</v>
+        <v>1.78125</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.042253521126761</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.323943661971831</v>
+        <v>4.488095238095238</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.366197183098592</v>
+        <v>5.571428571428571</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.896</v>
+        <v>73.51333333333334</v>
       </c>
       <c r="C3" t="n">
-        <v>73.14000000000001</v>
+        <v>73.69333333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>103.6368608148756</v>
+        <v>100.6423014293468</v>
       </c>
       <c r="E3" t="n">
-        <v>103.9103089964452</v>
+        <v>101.3207888547132</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4853420195439738</v>
+        <v>0.4734748010610079</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1653161963304461</v>
+        <v>0.1618247668952763</v>
       </c>
       <c r="H3" t="n">
-        <v>0.343915343915344</v>
+        <v>0.3305084745762712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.263843648208469</v>
+        <v>0.23342175066313</v>
       </c>
       <c r="J3" t="n">
-        <v>8.4</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="M3" t="n">
-        <v>6.2</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>10.8</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="O3" t="n">
-        <v>21</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3420195439739414</v>
+        <v>0.3554376657824934</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="R3" t="n">
-        <v>7.2</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1172638436482085</v>
+        <v>0.1007957559681698</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="U3" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05537459283387622</v>
+        <v>0.04774535809018567</v>
       </c>
       <c r="W3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1791530944625407</v>
+        <v>0.1830238726790451</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.8</v>
+        <v>19.66666666666667</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3061889250814332</v>
+        <v>0.3129973474801061</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5142857142857143</v>
+        <v>0.5223880597014925</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4444444444444445</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3454545454545455</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3085106382978723</v>
+        <v>0.3050847457627118</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.028571428571429</v>
+        <v>1.044776119402985</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9664429530201341</v>
+        <v>0.9144385026737968</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6363636363636365</v>
+        <v>0.6329113924050633</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5128205128205129</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.62962962962963</v>
+        <v>1.78125</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.042253521126761</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.323943661971832</v>
+        <v>4.488095238095238</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.366197183098592</v>
+        <v>5.571428571428571</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>366.9200000000001</v>
+        <v>443.2400000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>365.7</v>
+        <v>442.16</v>
       </c>
       <c r="D4" t="n">
-        <v>103.9103089964452</v>
+        <v>101.3207888547132</v>
       </c>
       <c r="E4" t="n">
-        <v>103.6368608148756</v>
+        <v>100.6423014293468</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4650455927051672</v>
+        <v>0.4526854219948849</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1476774366777052</v>
+        <v>0.1478736148547469</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3625498007968128</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2249240121580547</v>
+        <v>0.2404092071611253</v>
       </c>
       <c r="J4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L4" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="N4" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="O4" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3525835866261398</v>
+        <v>0.3682864450127877</v>
       </c>
       <c r="Q4" t="n">
         <v>24</v>
       </c>
       <c r="R4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1610942249240122</v>
+        <v>0.1406649616368287</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.04859335038363171</v>
       </c>
       <c r="W4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X4" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1975683890577508</v>
+        <v>0.1892583120204604</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2462006079027356</v>
+        <v>0.2531969309462916</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4482758620689655</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4528301886792453</v>
+        <v>0.4363636363636363</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3692307692307693</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2716049382716049</v>
+        <v>0.2626262626262627</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9027777777777778</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.142857142857143</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9452054794520548</v>
+        <v>0.9017341040462428</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.5492957746478874</v>
+        <v>0.4880952380952381</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.675</v>
+        <v>0.6593406593406593</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.75</v>
+        <v>1.585365853658537</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.075757575757576</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.984848484848484</v>
+        <v>4.949367088607595</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.060606060606061</v>
+        <v>5.949367088607595</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.38400000000001</v>
+        <v>73.87333333333335</v>
       </c>
       <c r="C5" t="n">
-        <v>73.14000000000001</v>
+        <v>73.69333333333334</v>
       </c>
       <c r="D5" t="n">
-        <v>103.9103089964452</v>
+        <v>101.3207888547132</v>
       </c>
       <c r="E5" t="n">
-        <v>103.6368608148756</v>
+        <v>100.6423014293468</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4650455927051672</v>
+        <v>0.4526854219948849</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1476774366777052</v>
+        <v>0.1478736148547469</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3625498007968127</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2249240121580547</v>
+        <v>0.2404092071611253</v>
       </c>
       <c r="J5" t="n">
-        <v>7.8</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>10.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="O5" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3525835866261398</v>
+        <v>0.3682864450127877</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>10.6</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1610942249240122</v>
+        <v>0.1406649616368286</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U5" t="n">
-        <v>2.8</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.04859335038363171</v>
       </c>
       <c r="W5" t="n">
-        <v>4.8</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1975683890577508</v>
+        <v>0.1892583120204603</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.4</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="AA5" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2462006079027356</v>
+        <v>0.2531969309462915</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.4482758620689655</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4528301886792453</v>
+        <v>0.4363636363636364</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.5263157894736843</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3692307692307692</v>
+        <v>0.3513513513513513</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.271604938271605</v>
+        <v>0.2626262626262626</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9027777777777778</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.142857142857143</v>
+        <v>1.052631578947369</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9452054794520548</v>
+        <v>0.9017341040462427</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.5492957746478874</v>
+        <v>0.4880952380952381</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.675</v>
+        <v>0.6593406593406593</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.75</v>
+        <v>1.585365853658537</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.075757575757576</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.984848484848485</v>
+        <v>4.949367088607596</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.060606060606061</v>
+        <v>5.949367088607596</v>
       </c>
     </row>
     <row r="7">
@@ -1429,64 +1429,64 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>59</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27</v>
+      </c>
+      <c r="H8" t="n">
         <v>5</v>
       </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" t="n">
+        <v>41</v>
+      </c>
+      <c r="K8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
         <v>13</v>
       </c>
-      <c r="E8" t="n">
-        <v>21</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>33</v>
-      </c>
-      <c r="K8" t="n">
-        <v>24</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>11</v>
-      </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="U8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1498,13 +1498,13 @@
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.706</v>
+        <v>0.7</v>
       </c>
       <c r="AB8" t="n">
         <v>1</v>
@@ -1528,63 +1528,63 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.438</v>
+        <v>0.381</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>132:55</t>
+          <t>163:40</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>55.08</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.573</v>
+        <v>0.529</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.532</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.908</v>
+        <v>0.863</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.073</v>
+        <v>0.098</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>3.154</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.727</v>
+        <v>3.923</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.727</v>
+        <v>7.077</v>
       </c>
       <c r="AX8" t="n">
         <v>0.193</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.172</v>
+        <v>0.187</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.314</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="9">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
         <v>29</v>
@@ -1768,13 +1768,13 @@
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -1783,37 +1783,37 @@
         <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="U10" t="n">
         <v>4</v>
@@ -1831,10 +1831,10 @@
         <v>4</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AB10" t="n">
         <v>2</v>
@@ -1858,63 +1858,63 @@
         <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AK10" t="n">
         <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>91:18</t>
+          <t>117:45</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>33.96</v>
+        <v>40.96</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.519</v>
+        <v>0.427</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.854</v>
+        <v>0.708</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.177</v>
+        <v>0.171</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.208</v>
+        <v>0.167</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.5</v>
+        <v>2.714</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>4.286</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.173</v>
+        <v>0.161</v>
       </c>
       <c r="AY10" t="n">
         <v>0.035</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.13</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="11">
@@ -1924,40 +1924,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
         <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -1966,46 +1966,46 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>13</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>56</v>
+      </c>
+      <c r="U11" t="n">
+        <v>10</v>
+      </c>
+      <c r="V11" t="n">
         <v>6</v>
       </c>
-      <c r="R11" t="n">
+      <c r="W11" t="n">
+        <v>18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y11" t="n">
         <v>10</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>46</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>15</v>
-      </c>
-      <c r="X11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>8</v>
-      </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.381</v>
+        <v>0.385</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2020,66 +2020,66 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AL11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.423</v>
+        <v>0.467</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>132:16</t>
+          <t>155:56</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>85.44</v>
+        <v>102.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.509</v>
+        <v>0.536</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.584</v>
+        <v>0.596</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.959</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.199</v>
+        <v>0.196</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.386</v>
+        <v>0.348</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.706</v>
+        <v>0.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.353</v>
+        <v>3.45</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.059</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.301</v>
+        <v>0.303</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.048</v>
+        <v>0.039</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.065</v>
+        <v>0.067</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.117</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="12">
@@ -2089,82 +2089,82 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>27</v>
-      </c>
-      <c r="L12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
       <c r="P12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" t="n">
         <v>6</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
+        <v>13</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>54</v>
+      </c>
+      <c r="U12" t="n">
         <v>4</v>
       </c>
-      <c r="R12" t="n">
+      <c r="V12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="n">
         <v>10</v>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>46</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>6</v>
-      </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.6</v>
+        <v>0.625</v>
       </c>
       <c r="AB12" t="n">
         <v>2</v>
@@ -2179,72 +2179,72 @@
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AH12" t="n">
         <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AK12" t="n">
         <v>1</v>
       </c>
       <c r="AL12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>124:45</t>
+          <t>154:02</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>33.64</v>
+        <v>45.52</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.6</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.615</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.011</v>
+        <v>0.923</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.16</v>
+        <v>0.118</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.167</v>
+        <v>4.25</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.5</v>
+        <v>4.625</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.126</v>
+        <v>0.137</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.093</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="13">
@@ -2254,37 +2254,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F13" t="n">
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H13" t="n">
         <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M13" t="n">
         <v>3</v>
@@ -2296,19 +2296,19 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U13" t="n">
         <v>7</v>
@@ -2323,13 +2323,13 @@
         <v>7</v>
       </c>
       <c r="Y13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.6</v>
+        <v>0.643</v>
       </c>
       <c r="AB13" t="n">
         <v>3</v>
@@ -2353,63 +2353,63 @@
         <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AK13" t="n">
         <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>120:30</t>
+          <t>138:52</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>51.36</v>
+        <v>58.8</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.514</v>
+        <v>0.512</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.993</v>
+        <v>0.969</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.117</v>
+        <v>0.119</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.351</v>
+        <v>0.302</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.167</v>
+        <v>6.143</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.833</v>
+        <v>6.857</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.198</v>
+        <v>0.196</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="14">
@@ -2419,22 +2419,22 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>17</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>5</v>
       </c>
-      <c r="C14" t="n">
-        <v>11</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -2446,10 +2446,10 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
@@ -2467,13 +2467,13 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
         <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2518,63 +2518,63 @@
         <v>1</v>
       </c>
       <c r="AI14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AK14" t="n">
         <v>4</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2</v>
-      </c>
       <c r="AL14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>23:06</t>
+          <t>38:27</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>10.88</v>
+        <v>16.88</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.536</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.619</v>
+        <v>0.571</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.011</v>
+        <v>1.007</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.184</v>
+        <v>0.118</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.25</v>
+        <v>0.143</v>
       </c>
       <c r="AU14" t="n">
         <v>0.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.219</v>
+        <v>0.203</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.046</v>
+        <v>0.053</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.165</v>
+        <v>0.124</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="15">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
         <v>27</v>
@@ -2758,7 +2758,7 @@
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
@@ -2797,13 +2797,13 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
+        <v>14</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>12</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>15</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2821,19 +2821,19 @@
         <v>7</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.438</v>
+        <v>0.389</v>
       </c>
       <c r="AB16" t="n">
         <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2864,47 +2864,47 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>69:25</t>
+          <t>77:38</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>29.92</v>
+        <v>32.92</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.45</v>
+        <v>0.391</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.484</v>
+        <v>0.437</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.902</v>
+        <v>0.82</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.067</v>
+        <v>0.061</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.45</v>
+        <v>0.391</v>
       </c>
       <c r="AU16" t="n">
         <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.201</v>
+        <v>0.196</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.076</v>
+        <v>0.092</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="17">
@@ -2914,22 +2914,22 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>17</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
         <v>5</v>
       </c>
-      <c r="C17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>4</v>
       </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -2941,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>4</v>
@@ -2956,19 +2956,19 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="U17" t="n">
         <v>3</v>
@@ -2983,93 +2983,93 @@
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>4</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>3</v>
-      </c>
       <c r="AI17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.3</v>
+        <v>0.364</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>63:36</t>
+          <t>72:30</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>20.88</v>
+        <v>24.88</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.306</v>
+        <v>0.381</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.318</v>
+        <v>0.388</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.575</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.096</v>
+        <v>0.121</v>
       </c>
       <c r="AT17" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AY17" t="n">
         <v>0.056</v>
       </c>
-      <c r="AU17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0.067</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="18">
@@ -3079,61 +3079,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M18" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" t="n">
         <v>4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="U18" t="n">
         <v>9</v>
@@ -3142,19 +3142,19 @@
         <v>11</v>
       </c>
       <c r="W18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.529</v>
+        <v>0.542</v>
       </c>
       <c r="AB18" t="n">
         <v>7</v>
@@ -3178,63 +3178,63 @@
         <v>3</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>174:10</t>
+        </is>
+      </c>
+      <c r="AO18" t="n">
+        <v>76.44</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AU18" t="n">
         <v>0.429</v>
       </c>
-      <c r="AK18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>145:01</t>
-        </is>
-      </c>
-      <c r="AO18" t="n">
-        <v>62.24</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AV18" t="n">
-        <v>7.833</v>
+        <v>8.286</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.333</v>
+        <v>8.714</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.2</v>
+        <v>0.203</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.164</v>
+        <v>0.17</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.029</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="19">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
         <v>19</v>
@@ -3259,7 +3259,7 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H19" t="n">
         <v>5</v>
@@ -3286,19 +3286,19 @@
         <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="U19" t="n">
         <v>3</v>
@@ -3343,63 +3343,63 @@
         <v>1</v>
       </c>
       <c r="AI19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.167</v>
+        <v>0.125</v>
       </c>
       <c r="AK19" t="n">
         <v>1</v>
       </c>
       <c r="AL19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM19" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>106:39</t>
+        </is>
+      </c>
+      <c r="AO19" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AU19" t="n">
         <v>0.091</v>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>96:47</t>
-        </is>
-      </c>
-      <c r="AO19" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0.1</v>
-      </c>
       <c r="AV19" t="n">
-        <v>3</v>
+        <v>3.091</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.1</v>
+        <v>3.182</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.207</v>
+        <v>0.208</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.059</v>
+        <v>0.054</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="20">
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3436,10 +3436,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3451,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -3574,159 +3574,159 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>379</v>
+        <v>445</v>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="E21" t="n">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="H21" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I21" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="J21" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="K21" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="L21" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="M21" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P21" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="R21" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>281</v>
+        <v>318</v>
       </c>
       <c r="U21" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="V21" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="W21" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="X21" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Y21" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="Z21" t="n">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.514</v>
+        <v>0.522</v>
       </c>
       <c r="AB21" t="n">
         <v>16</v>
       </c>
       <c r="AC21" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.444</v>
+        <v>0.421</v>
       </c>
       <c r="AE21" t="n">
         <v>7</v>
       </c>
       <c r="AF21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.412</v>
+        <v>0.389</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.345</v>
+        <v>0.304</v>
       </c>
       <c r="AK21" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AL21" t="n">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.309</v>
+        <v>0.305</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1000:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>429.48</v>
+        <v>519.08</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.485</v>
+        <v>0.473</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.529</v>
+        <v>0.511</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.882</v>
+        <v>0.857</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.165</v>
+        <v>0.162</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.264</v>
+        <v>0.233</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.042</v>
+        <v>1.083</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.324</v>
+        <v>4.488</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.366</v>
+        <v>5.571</v>
       </c>
       <c r="AX21" t="n">
         <v>0.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3739,159 +3739,159 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>380</v>
+        <v>448</v>
       </c>
       <c r="D22" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="E22" t="n">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
+        <v>173</v>
+      </c>
+      <c r="H22" t="n">
+        <v>94</v>
+      </c>
+      <c r="I22" t="n">
         <v>146</v>
       </c>
-      <c r="H22" t="n">
-        <v>74</v>
-      </c>
-      <c r="I22" t="n">
-        <v>118</v>
-      </c>
       <c r="J22" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K22" t="n">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="L22" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="M22" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P22" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="Q22" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R22" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="U22" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V22" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="W22" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="X22" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="Y22" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Z22" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.448</v>
+        <v>0.451</v>
       </c>
       <c r="AB22" t="n">
         <v>24</v>
       </c>
       <c r="AC22" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>99</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>1200:00</t>
+        </is>
+      </c>
+      <c r="AO22" t="n">
+        <v>534.24</v>
+      </c>
+      <c r="AP22" t="n">
         <v>0.453</v>
       </c>
-      <c r="AE22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>81</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>1000:00</t>
-        </is>
-      </c>
-      <c r="AO22" t="n">
-        <v>446.92</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0.465</v>
-      </c>
       <c r="AQ22" t="n">
-        <v>0.499</v>
+        <v>0.492</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.85</v>
+        <v>0.839</v>
       </c>
       <c r="AS22" t="n">
         <v>0.148</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.225</v>
+        <v>0.24</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.076</v>
+        <v>1</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.985</v>
+        <v>4.949</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.061</v>
+        <v>5.949</v>
       </c>
       <c r="AX22" t="n">
         <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.076</v>
+        <v>0.073</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.131</v>
+        <v>0.134</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>9.833</v>
       </c>
       <c r="D24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E24" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.667</v>
       </c>
       <c r="J24" t="n">
-        <v>6.6</v>
+        <v>6.833</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>5.333</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2</v>
+        <v>0.667</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
@@ -4002,49 +4002,49 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="R24" t="n">
-        <v>2.8</v>
+        <v>2.833</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.667</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="X24" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.4</v>
+        <v>2.333</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>3.333</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.706</v>
+        <v>0.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AD24" t="n">
         <v>0.5</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -4062,63 +4062,63 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="n">
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AL24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.437</v>
+        <v>0.381</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>26:35</t>
+          <t>27:16</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>11.016</v>
+        <v>11.4</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.573</v>
+        <v>0.529</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.532</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.908</v>
+        <v>0.863</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.073</v>
+        <v>0.098</v>
       </c>
       <c r="AU24" t="n">
-        <v>3</v>
+        <v>3.154</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.727</v>
+        <v>3.923</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.727</v>
+        <v>7.077</v>
       </c>
       <c r="AX24" t="n">
         <v>0.193</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.172</v>
+        <v>0.187</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.314</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="25">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -4293,88 +4293,88 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>5.8</v>
+        <v>4.833</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>3.333</v>
       </c>
       <c r="H26" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="R26" t="n">
-        <v>2.6</v>
+        <v>2.667</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="V26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="X26" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
@@ -4383,72 +4383,72 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AI26" t="n">
         <v>1</v>
       </c>
       <c r="AJ26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AO26" t="n">
+        <v>6.827</v>
+      </c>
+      <c r="AP26" t="n">
         <v>0.4</v>
       </c>
-      <c r="AK26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AO26" t="n">
-        <v>6.792</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>0.519</v>
+        <v>0.427</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.854</v>
+        <v>0.708</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.177</v>
+        <v>0.171</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.208</v>
+        <v>0.167</v>
       </c>
       <c r="AU26" t="n">
-        <v>2.5</v>
+        <v>2.714</v>
       </c>
       <c r="AV26" t="n">
-        <v>4</v>
+        <v>4.286</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.173</v>
+        <v>0.161</v>
       </c>
       <c r="AY26" t="n">
         <v>0.035</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.13</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="27">
@@ -4458,88 +4458,88 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>16.333</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
         <v>5</v>
       </c>
-      <c r="C27" t="n">
-        <v>16</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I27" t="n">
-        <v>5.2</v>
-      </c>
       <c r="J27" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K27" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="O27" t="n">
         <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>3.4</v>
+        <v>3.333</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>2.167</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.667</v>
       </c>
       <c r="V27" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
         <v>3</v>
       </c>
       <c r="X27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.6</v>
+        <v>1.667</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.2</v>
+        <v>4.333</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.381</v>
+        <v>0.385</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4548,72 +4548,72 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="AJ27" t="n">
         <v>0.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.2</v>
+        <v>2.333</v>
       </c>
       <c r="AL27" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.423</v>
+        <v>0.467</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>26:27</t>
+          <t>25:59</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>17.088</v>
+        <v>17.033</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.509</v>
+        <v>0.536</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.584</v>
+        <v>0.596</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.959</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.199</v>
+        <v>0.196</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.386</v>
+        <v>0.348</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.706</v>
+        <v>0.75</v>
       </c>
       <c r="AV27" t="n">
-        <v>3.353</v>
+        <v>3.45</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.059</v>
+        <v>4.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.301</v>
+        <v>0.303</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.048</v>
+        <v>0.039</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.065</v>
+        <v>0.067</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.117</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="28">
@@ -4623,162 +4623,162 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>1.8</v>
+        <v>2.167</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2</v>
+        <v>3.833</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>2.167</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="V28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="X28" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.2</v>
+        <v>1.667</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>2.667</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.6</v>
+        <v>0.625</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AD28" t="n">
         <v>0.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AG28" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>24:57</t>
+          <t>25:40</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>6.728</v>
+        <v>7.587</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.6</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.615</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.011</v>
+        <v>0.923</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.16</v>
+        <v>0.118</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.167</v>
+        <v>4.25</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.5</v>
+        <v>4.625</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.126</v>
+        <v>0.137</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.093</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="29">
@@ -4788,162 +4788,162 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="D29" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.8</v>
-      </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>4.167</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="V29" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="X29" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>2.333</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.6</v>
+        <v>0.643</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AD29" t="n">
         <v>0.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AG29" t="n">
         <v>0.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AJ29" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AK29" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK29" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AL29" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>24:06</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>10.272</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.514</v>
+        <v>0.512</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.993</v>
+        <v>0.969</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.117</v>
+        <v>0.119</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.351</v>
+        <v>0.302</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AV29" t="n">
-        <v>6.167</v>
+        <v>6.143</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.833</v>
+        <v>6.857</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.198</v>
+        <v>0.196</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="30">
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>2.2</v>
+        <v>2.833</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -4965,28 +4965,28 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="G30" t="n">
-        <v>1.6</v>
+        <v>2.333</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4995,31 +4995,31 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="R30" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -5049,66 +5049,66 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.8</v>
+        <v>1.167</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.25</v>
+        <v>0.143</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.8</v>
+        <v>1.167</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>04:37</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>2.176</v>
+        <v>2.813</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.536</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.619</v>
+        <v>0.571</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.011</v>
+        <v>1.007</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.184</v>
+        <v>0.118</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.25</v>
+        <v>0.143</v>
       </c>
       <c r="AU30" t="n">
         <v>0.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.219</v>
+        <v>0.203</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.046</v>
+        <v>0.053</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.165</v>
+        <v>0.124</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="31">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>00:04</t>
+          <t>00:03</t>
         </is>
       </c>
       <c r="AO31" t="n">
@@ -5283,16 +5283,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="D32" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3.833</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -5301,79 +5301,79 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="K32" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>1</v>
       </c>
-      <c r="M32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>15</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="X32" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.437</v>
+        <v>0.389</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AG32" t="n">
         <v>0.5</v>
@@ -5398,47 +5398,47 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>5.984</v>
+        <v>5.487</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.45</v>
+        <v>0.391</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.484</v>
+        <v>0.437</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.902</v>
+        <v>0.82</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.067</v>
+        <v>0.061</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.45</v>
+        <v>0.391</v>
       </c>
       <c r="AU32" t="n">
         <v>1</v>
       </c>
       <c r="AV32" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.201</v>
+        <v>0.196</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.076</v>
+        <v>0.092</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="33">
@@ -5448,83 +5448,83 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>2.4</v>
+        <v>2.833</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G33" t="n">
-        <v>2.8</v>
+        <v>2.667</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="I33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA33" t="n">
         <v>0.4</v>
       </c>
-      <c r="J33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>-3</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
@@ -5544,66 +5544,66 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AI33" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.3</v>
+        <v>0.364</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="AM33" t="n">
         <v>0</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>4.176</v>
+        <v>4.147</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.306</v>
+        <v>0.381</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.318</v>
+        <v>0.388</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.575</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.096</v>
+        <v>0.121</v>
       </c>
       <c r="AT33" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AY33" t="n">
         <v>0.056</v>
       </c>
-      <c r="AU33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0.067</v>
-      </c>
       <c r="AZ33" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="34">
@@ -5613,162 +5613,162 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>13.2</v>
+        <v>13.333</v>
       </c>
       <c r="D34" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E34" t="n">
-        <v>6.6</v>
+        <v>6.667</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>3.4</v>
+        <v>3.333</v>
       </c>
       <c r="I34" t="n">
-        <v>4.2</v>
+        <v>4.333</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K34" t="n">
-        <v>5</v>
+        <v>5.167</v>
       </c>
       <c r="L34" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="R34" t="n">
-        <v>1.6</v>
+        <v>1.667</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="U34" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>2.2</v>
+        <v>1.833</v>
       </c>
       <c r="W34" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="X34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.8</v>
+        <v>2.167</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.529</v>
+        <v>0.542</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.8</v>
+        <v>2.333</v>
       </c>
       <c r="AD34" t="n">
         <v>0.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AG34" t="n">
         <v>0.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AJ34" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>29:01</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AU34" t="n">
         <v>0.429</v>
       </c>
-      <c r="AK34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>29:00</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>12.448</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AV34" t="n">
-        <v>7.833</v>
+        <v>8.286</v>
       </c>
       <c r="AW34" t="n">
-        <v>8.333</v>
+        <v>8.714</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.2</v>
+        <v>0.203</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.164</v>
+        <v>0.17</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.029</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="35">
@@ -5778,40 +5778,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>3.8</v>
+        <v>3.167</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="E35" t="n">
-        <v>2.6</v>
+        <v>2.167</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="G35" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H35" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="I35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1.2</v>
-      </c>
       <c r="L35" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5820,25 +5820,25 @@
         <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="U35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V35" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -5847,10 +5847,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AA35" t="n">
         <v>0.2</v>
@@ -5859,81 +5859,81 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AG35" t="n">
         <v>0.6</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="AJ35" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AK35" t="n">
         <v>0.167</v>
       </c>
-      <c r="AK35" t="n">
-        <v>0.2</v>
-      </c>
       <c r="AL35" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="AM35" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>8.013</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AU35" t="n">
         <v>0.091</v>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>8.616</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0.1</v>
-      </c>
       <c r="AV35" t="n">
-        <v>3</v>
+        <v>3.091</v>
       </c>
       <c r="AW35" t="n">
-        <v>3.1</v>
+        <v>3.182</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.207</v>
+        <v>0.208</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.059</v>
+        <v>0.054</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="36">
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -5973,7 +5973,7 @@
         <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5985,10 +5985,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -6108,118 +6108,118 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>75.8</v>
+        <v>74.167</v>
       </c>
       <c r="D37" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="E37" t="n">
-        <v>31.6</v>
+        <v>31.667</v>
       </c>
       <c r="F37" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="G37" t="n">
-        <v>29.8</v>
+        <v>31.167</v>
       </c>
       <c r="H37" t="n">
-        <v>16.2</v>
+        <v>14.667</v>
       </c>
       <c r="I37" t="n">
-        <v>23.4</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>14.8</v>
+        <v>15.167</v>
       </c>
       <c r="K37" t="n">
-        <v>26</v>
+        <v>26.667</v>
       </c>
       <c r="L37" t="n">
         <v>13</v>
       </c>
       <c r="M37" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2</v>
+        <v>3.167</v>
       </c>
       <c r="O37" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P37" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.2</v>
+        <v>6.667</v>
       </c>
       <c r="R37" t="n">
-        <v>22.2</v>
+        <v>22.833</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>281</v>
+        <v>318</v>
       </c>
       <c r="U37" t="n">
-        <v>8.4</v>
+        <v>8.333</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>6.667</v>
       </c>
       <c r="W37" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X37" t="n">
-        <v>5.4</v>
+        <v>5.333</v>
       </c>
       <c r="Y37" t="n">
-        <v>10.8</v>
+        <v>11.667</v>
       </c>
       <c r="Z37" t="n">
-        <v>21</v>
+        <v>22.333</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.514</v>
+        <v>0.522</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.2</v>
+        <v>2.667</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.2</v>
+        <v>6.333</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.444</v>
+        <v>0.421</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="AF37" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.412</v>
+        <v>0.389</v>
       </c>
       <c r="AH37" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.345</v>
+        <v>0.304</v>
       </c>
       <c r="AK37" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AL37" t="n">
-        <v>18.8</v>
+        <v>19.667</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.309</v>
+        <v>0.305</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6227,40 +6227,40 @@
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>85.896</v>
+        <v>86.51300000000001</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.485</v>
+        <v>0.473</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.529</v>
+        <v>0.511</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.882</v>
+        <v>0.857</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.165</v>
+        <v>0.162</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.264</v>
+        <v>0.233</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.042</v>
+        <v>1.083</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.324</v>
+        <v>4.488</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.366</v>
+        <v>5.571</v>
       </c>
       <c r="AX37" t="n">
         <v>0.2</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="BA37" t="n">
         <v>0</v>
@@ -6273,159 +6273,159 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>76</v>
+        <v>74.667</v>
       </c>
       <c r="D38" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="E38" t="n">
-        <v>36.6</v>
+        <v>36.333</v>
       </c>
       <c r="F38" t="n">
-        <v>9.199999999999999</v>
+        <v>8.667</v>
       </c>
       <c r="G38" t="n">
-        <v>29.2</v>
+        <v>28.833</v>
       </c>
       <c r="H38" t="n">
-        <v>14.8</v>
+        <v>15.667</v>
       </c>
       <c r="I38" t="n">
-        <v>23.6</v>
+        <v>24.333</v>
       </c>
       <c r="J38" t="n">
-        <v>14.2</v>
+        <v>13.167</v>
       </c>
       <c r="K38" t="n">
-        <v>24.8</v>
+        <v>26.333</v>
       </c>
       <c r="L38" t="n">
-        <v>16</v>
+        <v>15.167</v>
       </c>
       <c r="M38" t="n">
-        <v>8</v>
+        <v>7.333</v>
       </c>
       <c r="N38" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P38" t="n">
-        <v>13.2</v>
+        <v>13.167</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.4</v>
+        <v>5.667</v>
       </c>
       <c r="R38" t="n">
-        <v>22.8</v>
+        <v>22.333</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="U38" t="n">
-        <v>7.8</v>
+        <v>6.833</v>
       </c>
       <c r="V38" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="W38" t="n">
-        <v>9.800000000000001</v>
+        <v>10.833</v>
       </c>
       <c r="X38" t="n">
-        <v>5.6</v>
+        <v>6.833</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.4</v>
+        <v>10.833</v>
       </c>
       <c r="Z38" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.448</v>
+        <v>0.451</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AC38" t="n">
-        <v>10.6</v>
+        <v>9.167</v>
       </c>
       <c r="AD38" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>12.333</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>200:00</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="AP38" t="n">
         <v>0.453</v>
       </c>
-      <c r="AE38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO38" t="n">
-        <v>89.384</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.465</v>
-      </c>
       <c r="AQ38" t="n">
-        <v>0.499</v>
+        <v>0.492</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.85</v>
+        <v>0.839</v>
       </c>
       <c r="AS38" t="n">
         <v>0.148</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.225</v>
+        <v>0.24</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.076</v>
+        <v>1</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.985</v>
+        <v>4.949</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.061</v>
+        <v>5.949</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.208</v>
+        <v>0.206</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.118</v>
+        <v>0.126</v>
       </c>
       <c r="BA38" t="n">
         <v>0</v>
